--- a/Models/Птицы/results/Птица - Результаты прогнозов Prophet.xlsx
+++ b/Models/Птицы/results/Птица - Результаты прогнозов Prophet.xlsx
@@ -478,31 +478,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1416.91</v>
+        <v>1124.42</v>
       </c>
       <c r="E2" t="n">
-        <v>1133.93</v>
+        <v>1039.91</v>
       </c>
       <c r="F2" t="n">
-        <v>11.74</v>
+        <v>10.21</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>[11017.33, 9581.39, 12312.82]</t>
+          <t>[11436.06, 11602.03, 10686.71]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[8963.23, 9586.12, 10969.85]</t>
+          <t>[10080.07, 10273.59, 10251.41]</t>
         </is>
       </c>
     </row>
@@ -514,31 +514,31 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1081.75</v>
+        <v>1782.69</v>
       </c>
       <c r="E3" t="n">
-        <v>913.22</v>
+        <v>1465.22</v>
       </c>
       <c r="F3" t="n">
-        <v>8.449999999999999</v>
+        <v>15.95</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>[9387.06, 11891.14, 9275.67]</t>
+          <t>[11530.16, 10590.5, 11465.21]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[9586.12, 10969.85, 10894.97]</t>
+          <t>[10273.59, 10251.41, 8665.21]</t>
         </is>
       </c>
     </row>
@@ -550,31 +550,31 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1087.12</v>
+        <v>1891.91</v>
       </c>
       <c r="E4" t="n">
-        <v>979.64</v>
+        <v>1601.91</v>
       </c>
       <c r="F4" t="n">
-        <v>9.039999999999999</v>
+        <v>16.67</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>[12026.85, 9380.67, 10606.59]</t>
+          <t>[10552.98, 11418.96, 13189.14]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[10969.85, 10894.97, 10238.97]</t>
+          <t>[10251.41, 8665.21, 11438.74]</t>
         </is>
       </c>
     </row>
@@ -586,31 +586,31 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1372.88</v>
+        <v>1980.84</v>
       </c>
       <c r="E5" t="n">
-        <v>1209.78</v>
+        <v>1870.57</v>
       </c>
       <c r="F5" t="n">
-        <v>10.4</v>
+        <v>20.04</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>[9324.72, 10537.5, 10931.91]</t>
+          <t>[11397.65, 13161.14, 9717.16]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[10894.97, 10238.97, 12692.46]</t>
+          <t>[8665.21, 11438.74, 8560.3]</t>
         </is>
       </c>
     </row>
@@ -622,31 +622,31 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>964.16</v>
+        <v>1634.74</v>
       </c>
       <c r="E6" t="n">
-        <v>684.26</v>
+        <v>1539.66</v>
       </c>
       <c r="F6" t="n">
-        <v>5.66</v>
+        <v>13.77</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>[10650.87, 11074.23, 10356.51]</t>
+          <t>[12903.79, 9467.5, 10304.79]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[10238.97, 12692.46, 10379.17]</t>
+          <t>[11438.74, 8560.3, 12551.51]</t>
         </is>
       </c>
     </row>
@@ -658,31 +658,31 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1182.44</v>
+        <v>1519.79</v>
       </c>
       <c r="E7" t="n">
-        <v>980.34</v>
+        <v>1381.35</v>
       </c>
       <c r="F7" t="n">
-        <v>8.58</v>
+        <v>12.13</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>[11028.59, 10293.09, 11271.13]</t>
+          <t>[9440.32, 10276.09, 11396.69]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[12692.46, 10379.17, 10080.07]</t>
+          <t>[8560.3, 12551.51, 12385.3]</t>
         </is>
       </c>
     </row>
@@ -694,31 +694,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1059.51</v>
+        <v>2022.02</v>
       </c>
       <c r="E8" t="n">
-        <v>871.37</v>
+        <v>1933.61</v>
       </c>
       <c r="F8" t="n">
-        <v>8.56</v>
+        <v>15.22</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>[10398.33, 11391.94, 11556.67]</t>
+          <t>[10205.65, 11288.0, 10658.24]</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[10379.17, 10080.07, 10273.59]</t>
+          <t>[12551.51, 12385.3, 13015.9]</t>
         </is>
       </c>
     </row>
@@ -730,31 +730,31 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1124.42</v>
+        <v>1359.34</v>
       </c>
       <c r="E9" t="n">
-        <v>1039.91</v>
+        <v>1116.63</v>
       </c>
       <c r="F9" t="n">
-        <v>10.21</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>[11436.06, 11602.03, 10686.71]</t>
+          <t>[11468.13, 10865.96, 10891.78]</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[10080.07, 10273.59, 10251.41]</t>
+          <t>[12385.3, 13015.9, 10609.0]</t>
         </is>
       </c>
     </row>
@@ -766,31 +766,31 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1782.69</v>
+        <v>1387.42</v>
       </c>
       <c r="E10" t="n">
-        <v>1465.22</v>
+        <v>1194.36</v>
       </c>
       <c r="F10" t="n">
-        <v>15.95</v>
+        <v>10.11</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>[11530.16, 10590.5, 11465.21]</t>
+          <t>[10929.0, 10969.56, 11544.24]</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[10273.59, 10251.41, 8665.21]</t>
+          <t>[13015.9, 10609.0, 10408.6]</t>
         </is>
       </c>
     </row>
@@ -802,31 +802,31 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1891.91</v>
+        <v>824.99</v>
       </c>
       <c r="E11" t="n">
-        <v>1601.91</v>
+        <v>743.98</v>
       </c>
       <c r="F11" t="n">
-        <v>16.67</v>
+        <v>7.08</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>[10552.98, 11418.96, 13189.14]</t>
+          <t>[11075.5, 11655.89, 11157.85]</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>[10251.41, 8665.21, 11438.74]</t>
+          <t>[10609.0, 10408.6, 10639.7]</t>
         </is>
       </c>
     </row>
@@ -838,31 +838,31 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>45.31</v>
+        <v>30</v>
       </c>
       <c r="E12" t="n">
-        <v>40.09</v>
+        <v>29.07</v>
       </c>
       <c r="F12" t="n">
-        <v>56.42</v>
+        <v>580.61</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>[42.06, 28.22, 12.66]</t>
+          <t>[29.21, 28.02, 43.4]</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>[64.3, 56.5, 82.4]</t>
+          <t>[68.4, 1.6, 65.0]</t>
         </is>
       </c>
     </row>
@@ -874,31 +874,31 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>46.33</v>
+        <v>19.79</v>
       </c>
       <c r="E13" t="n">
-        <v>41.84</v>
+        <v>16.99</v>
       </c>
       <c r="F13" t="n">
-        <v>61.97</v>
+        <v>573.9</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>[28.8, 12.42, 25.75]</t>
+          <t>[28.55, 44.05, 58.24]</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>[56.5, 82.4, 53.6]</t>
+          <t>[1.6, 65.0, 61.3]</t>
         </is>
       </c>
     </row>
@@ -910,31 +910,31 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>42.9</v>
+        <v>81.39</v>
       </c>
       <c r="E14" t="n">
-        <v>33.2</v>
+        <v>57.05</v>
       </c>
       <c r="F14" t="n">
-        <v>47.97</v>
+        <v>35.11</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>[12.96, 27.45, 32.98]</t>
+          <t>[40.47, 53.29, 115.6]</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>[82.4, 53.6, 37.0]</t>
+          <t>[65.0, 61.3, 254.2]</t>
         </is>
       </c>
     </row>
@@ -946,31 +946,31 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>23.49</v>
+        <v>78.95999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>20.15</v>
+        <v>53.19</v>
       </c>
       <c r="F15" t="n">
-        <v>41.56</v>
+        <v>32.09</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>[27.91, 33.62, 15.03]</t>
+          <t>[54.69, 118.71, 36.83]</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[53.6, 37.0, 46.4]</t>
+          <t>[61.3, 254.2, 54.3]</t>
         </is>
       </c>
     </row>
@@ -982,31 +982,31 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>29.41</v>
+        <v>77.8</v>
       </c>
       <c r="E16" t="n">
-        <v>24.52</v>
+        <v>50.82</v>
       </c>
       <c r="F16" t="n">
-        <v>49.84</v>
+        <v>30.01</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>[34.82, 15.3, 12.32]</t>
+          <t>[120.51, 37.51, 28.51]</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>[37.0, 46.4, 52.6]</t>
+          <t>[254.2, 54.3, 30.5]</t>
         </is>
       </c>
     </row>
@@ -1018,31 +1018,31 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>37.67</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>37.4</v>
+        <v>7.49</v>
       </c>
       <c r="F17" t="n">
-        <v>67.73999999999999</v>
+        <v>20.23</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>[15.34, 12.43, 27.42]</t>
+          <t>[37.76, 29.32, 13.25]</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>[46.4, 52.6, 68.4]</t>
+          <t>[54.3, 30.5, 18.0]</t>
         </is>
       </c>
     </row>
@@ -1054,31 +1054,31 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>35.83</v>
+        <v>13.46</v>
       </c>
       <c r="E18" t="n">
-        <v>35.15</v>
+        <v>9.84</v>
       </c>
       <c r="F18" t="n">
-        <v>572.15</v>
+        <v>26.92</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>[12.7, 28.16, 26.91]</t>
+          <t>[28.76, 12.89, 25.91]</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>[52.6, 68.4, 1.6]</t>
+          <t>[30.5, 18.0, 48.6]</t>
         </is>
       </c>
     </row>
@@ -1090,31 +1090,31 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>30</v>
+        <v>13.5</v>
       </c>
       <c r="E19" t="n">
-        <v>29.07</v>
+        <v>10.79</v>
       </c>
       <c r="F19" t="n">
-        <v>580.61</v>
+        <v>31.69</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>[29.21, 28.02, 43.4]</t>
+          <t>[12.87, 26.33, 28.85]</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>[68.4, 1.6, 65.0]</t>
+          <t>[18.0, 48.6, 23.9]</t>
         </is>
       </c>
     </row>
@@ -1126,31 +1126,31 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>19.79</v>
+        <v>26.29</v>
       </c>
       <c r="E20" t="n">
-        <v>16.99</v>
+        <v>22.17</v>
       </c>
       <c r="F20" t="n">
-        <v>573.9</v>
+        <v>47</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>[28.55, 44.05, 58.24]</t>
+          <t>[26.06, 28.6, 13.12]</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>[1.6, 65.0, 61.3]</t>
+          <t>[48.6, 23.9, 52.4]</t>
         </is>
       </c>
     </row>
@@ -1162,31 +1162,31 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>81.39</v>
+        <v>36.04</v>
       </c>
       <c r="E21" t="n">
-        <v>57.05</v>
+        <v>31.04</v>
       </c>
       <c r="F21" t="n">
-        <v>35.11</v>
+        <v>59.44</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>[40.47, 53.29, 115.6]</t>
+          <t>[29.7, 13.79, 11.9]</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>[65.0, 61.3, 254.2]</t>
+          <t>[23.9, 52.4, 60.6]</t>
         </is>
       </c>
     </row>
@@ -1198,31 +1198,31 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2015.33</v>
+        <v>1260.98</v>
       </c>
       <c r="E22" t="n">
-        <v>1935</v>
+        <v>1223.23</v>
       </c>
       <c r="F22" t="n">
-        <v>16.58</v>
+        <v>10.86</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>[9413.82, 9006.66, 10253.22]</t>
+          <t>[10056.99, 9718.9, 10112.76]</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>[11949.02, 10187.92, 12341.77]</t>
+          <t>[11018.07, 10774.72, 11765.56]</t>
         </is>
       </c>
     </row>
@@ -1234,31 +1234,31 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1422.12</v>
+        <v>1907.85</v>
       </c>
       <c r="E23" t="n">
-        <v>1383.86</v>
+        <v>1772.2</v>
       </c>
       <c r="F23" t="n">
-        <v>12.11</v>
+        <v>14.85</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>[9129.24, 10509.41, 10099.4]</t>
+          <t>[9767.93, 10166.85, 9835.36]</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>[10187.92, 12341.77, 11359.95]</t>
+          <t>[10774.72, 11765.56, 12546.48]</t>
         </is>
       </c>
     </row>
@@ -1270,31 +1270,31 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1594.98</v>
+        <v>1820.56</v>
       </c>
       <c r="E24" t="n">
-        <v>1568.2</v>
+        <v>1721.7</v>
       </c>
       <c r="F24" t="n">
-        <v>13.36</v>
+        <v>14.06</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>[10646.99, 10194.23, 9620.12]</t>
+          <t>[10329.15, 10000.8, 11024.93]</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>[12341.77, 11359.95, 11464.21]</t>
+          <t>[11765.56, 12546.48, 12207.96]</t>
         </is>
       </c>
     </row>
@@ -1306,31 +1306,31 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1230.45</v>
+        <v>1583.18</v>
       </c>
       <c r="E25" t="n">
-        <v>1063.18</v>
+        <v>1449.52</v>
       </c>
       <c r="F25" t="n">
-        <v>9.33</v>
+        <v>11.75</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>[10240.28, 9672.25, 10814.0]</t>
+          <t>[10200.4, 11278.55, 13096.4]</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>[11359.95, 11464.21, 11091.93]</t>
+          <t>[12546.48, 12207.96, 12023.33]</t>
         </is>
       </c>
     </row>
@@ -1342,31 +1342,31 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1974.37</v>
+        <v>926.3200000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>1646.76</v>
+        <v>897.7</v>
       </c>
       <c r="F26" t="n">
-        <v>13.81</v>
+        <v>7.67</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>[9686.47, 10839.8, 9401.54]</t>
+          <t>[11485.21, 13243.74, 11571.05]</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>[11464.21, 11091.93, 12311.95]</t>
+          <t>[12207.96, 12023.33, 10821.1]</t>
         </is>
       </c>
     </row>
@@ -1378,31 +1378,31 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1785</v>
+        <v>872.74</v>
       </c>
       <c r="E27" t="n">
-        <v>1415.48</v>
+        <v>777.5700000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>11.94</v>
+        <v>6.68</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>[10901.69, 9478.84, 9794.97]</t>
+          <t>[13264.08, 11640.36, 13025.66]</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>[11091.93, 12311.95, 11018.07]</t>
+          <t>[12023.33, 10821.1, 12752.96]</t>
         </is>
       </c>
     </row>
@@ -1414,31 +1414,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1920.58</v>
+        <v>721.8099999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>1726.53</v>
+        <v>656.59</v>
       </c>
       <c r="F28" t="n">
-        <v>14.83</v>
+        <v>5.49</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>[9399.07, 9962.11, 9563.97]</t>
+          <t>[11756.81, 12993.54, 12553.34]</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>[12311.95, 11018.07, 10774.72]</t>
+          <t>[10821.1, 12752.96, 13346.82]</t>
         </is>
       </c>
     </row>
@@ -1450,31 +1450,31 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1260.98</v>
+        <v>618.4</v>
       </c>
       <c r="E29" t="n">
-        <v>1223.23</v>
+        <v>523.49</v>
       </c>
       <c r="F29" t="n">
-        <v>10.86</v>
+        <v>4.14</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>[10056.99, 9718.9, 10112.76]</t>
+          <t>[12857.23, 12438.36, 12176.94]</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>[11018.07, 10774.72, 11765.56]</t>
+          <t>[12752.96, 13346.82, 11619.21]</t>
         </is>
       </c>
     </row>
@@ -1486,31 +1486,31 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1907.85</v>
+        <v>1629.78</v>
       </c>
       <c r="E30" t="n">
-        <v>1772.2</v>
+        <v>1363.77</v>
       </c>
       <c r="F30" t="n">
-        <v>14.85</v>
+        <v>12.25</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>[9767.93, 10166.85, 9835.36]</t>
+          <t>[12580.68, 12319.22, 13130.31]</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>[10774.72, 11765.56, 12546.48]</t>
+          <t>[13346.82, 11619.21, 10505.14]</t>
         </is>
       </c>
     </row>
@@ -1522,31 +1522,31 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1820.56</v>
+        <v>1792.7</v>
       </c>
       <c r="E31" t="n">
-        <v>1721.7</v>
+        <v>1602.17</v>
       </c>
       <c r="F31" t="n">
-        <v>14.06</v>
+        <v>14.89</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>[10329.15, 10000.8, 11024.93]</t>
+          <t>[12374.03, 13188.04, 12213.04]</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>[11765.56, 12546.48, 12207.96]</t>
+          <t>[11619.21, 10505.14, 10844.25]</t>
         </is>
       </c>
     </row>
@@ -1558,16 +1558,16 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.01]</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.11]</t>
+          <t>[0.01, 0.01, 0.11]</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1634,19 +1634,19 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>9.76</v>
+        <v>0.24</v>
       </c>
       <c r="E34" t="n">
-        <v>5.68</v>
+        <v>0.17</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1655,12 +1655,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>[0.0, 0.13, 16.9]</t>
+          <t>[0.01, 0.1, 0.2]</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.6]</t>
         </is>
       </c>
     </row>
@@ -1672,19 +1672,19 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>9.69</v>
+        <v>0.25</v>
       </c>
       <c r="E35" t="n">
-        <v>5.64</v>
+        <v>0.17</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1693,12 +1693,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>[0.12, 16.79, 0.01]</t>
+          <t>[0.09, 0.17, 0.0]</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.6, 0.0]</t>
         </is>
       </c>
     </row>
@@ -1710,19 +1710,19 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>14.56</v>
+        <v>0.25</v>
       </c>
       <c r="E36" t="n">
-        <v>8.41</v>
+        <v>0.15</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1731,12 +1731,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>[25.22, 0.01, 0.0]</t>
+          <t>[0.16, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.6, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>[0.01, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1786,19 +1786,19 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.03]</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1824,19 +1824,19 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.01</v>
+        <v>1.26</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>0.74</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.01]</t>
+          <t>[0.0, 0.03, 2.18]</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1862,19 +1862,19 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.06</v>
+        <v>0.52</v>
       </c>
       <c r="E40" t="n">
-        <v>0.04</v>
+        <v>0.3</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>[0.01, 0.01, 0.11]</t>
+          <t>[0.02, 0.89, 0.0]</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1900,19 +1900,19 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.24</v>
+        <v>1.29</v>
       </c>
       <c r="E41" t="n">
-        <v>0.17</v>
+        <v>0.74</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1921,12 +1921,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>[0.01, 0.1, 0.2]</t>
+          <t>[2.23, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.6]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -1938,31 +1938,31 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>111.73</v>
+        <v>694.48</v>
       </c>
       <c r="E42" t="n">
-        <v>96.11</v>
+        <v>648.11</v>
       </c>
       <c r="F42" t="n">
-        <v>1.49</v>
+        <v>10.9</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>[6424.72, 5856.88, 6498.84]</t>
+          <t>[6460.3, 6325.05, 7074.59]</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>[6353.35, 5898.97, 6673.73]</t>
+          <t>[6144.41, 5613.89, 6157.31]</t>
         </is>
       </c>
     </row>
@@ -1974,31 +1974,31 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>113.74</v>
+        <v>1182.04</v>
       </c>
       <c r="E43" t="n">
-        <v>95.63</v>
+        <v>1095.33</v>
       </c>
       <c r="F43" t="n">
-        <v>1.48</v>
+        <v>18.32</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>[5855.22, 6491.59, 6156.89]</t>
+          <t>[6294.88, 7050.63, 7755.48]</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>[5898.97, 6673.73, 6217.87]</t>
+          <t>[5613.89, 6157.31, 6043.79]</t>
         </is>
       </c>
     </row>
@@ -2010,31 +2010,31 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>272.04</v>
+        <v>1720.32</v>
       </c>
       <c r="E44" t="n">
-        <v>205.63</v>
+        <v>1598.41</v>
       </c>
       <c r="F44" t="n">
-        <v>3</v>
+        <v>26.46</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>[6532.89, 6190.64, 6507.64]</t>
+          <t>[6966.13, 7663.78, 8364.6]</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>[6673.73, 6217.87, 6956.45]</t>
+          <t>[6157.31, 6043.79, 5998.19]</t>
         </is>
       </c>
     </row>
@@ -2046,31 +2046,31 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>325.52</v>
+        <v>1644.69</v>
       </c>
       <c r="E45" t="n">
-        <v>266.32</v>
+        <v>1416.84</v>
       </c>
       <c r="F45" t="n">
-        <v>4.03</v>
+        <v>23.45</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>[6215.11, 6536.92, 5887.62]</t>
+          <t>[7640.2, 8336.26, 6693.0]</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>[6217.87, 6956.45, 6264.3]</t>
+          <t>[6043.79, 5998.19, 6376.96]</t>
         </is>
       </c>
     </row>
@@ -2082,31 +2082,31 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>342.1</v>
+        <v>1361.03</v>
       </c>
       <c r="E46" t="n">
-        <v>333.82</v>
+        <v>1068.86</v>
       </c>
       <c r="F46" t="n">
-        <v>5.21</v>
+        <v>18.09</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>[6549.37, 5901.01, 6057.44]</t>
+          <t>[8208.1, 6577.9, 6370.54]</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>[6956.45, 6264.3, 5826.35]</t>
+          <t>[5998.19, 6376.96, 5574.81]</t>
         </is>
       </c>
     </row>
@@ -2118,31 +2118,31 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>311.59</v>
+        <v>440.01</v>
       </c>
       <c r="E47" t="n">
-        <v>311.12</v>
+        <v>372.91</v>
       </c>
       <c r="F47" t="n">
-        <v>5.12</v>
+        <v>6.33</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>[5953.31, 6116.53, 6476.6]</t>
+          <t>[6476.58, 6245.0, 6818.25]</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>[6264.3, 5826.35, 6144.41]</t>
+          <t>[6376.96, 5574.81, 6469.33]</t>
         </is>
       </c>
     </row>
@@ -2154,31 +2154,31 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>573.33</v>
+        <v>425.56</v>
       </c>
       <c r="E48" t="n">
-        <v>539.89</v>
+        <v>371.88</v>
       </c>
       <c r="F48" t="n">
-        <v>9.31</v>
+        <v>6.28</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>[6203.67, 6575.81, 6424.85]</t>
+          <t>[6221.36, 6791.2, 6633.3]</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>[5826.35, 6144.41, 5613.89]</t>
+          <t>[5574.81, 6469.33, 6486.09]</t>
         </is>
       </c>
     </row>
@@ -2190,31 +2190,31 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>694.48</v>
+        <v>365.66</v>
       </c>
       <c r="E49" t="n">
-        <v>648.11</v>
+        <v>281.95</v>
       </c>
       <c r="F49" t="n">
-        <v>10.9</v>
+        <v>4.48</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>[6460.3, 6325.05, 7074.59]</t>
+          <t>[6683.73, 6522.73, 6816.65]</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>[6144.41, 5613.89, 6157.31]</t>
+          <t>[6469.33, 6486.09, 6221.83]</t>
         </is>
       </c>
     </row>
@@ -2226,31 +2226,31 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1182.04</v>
+        <v>328.32</v>
       </c>
       <c r="E50" t="n">
-        <v>1095.33</v>
+        <v>197.78</v>
       </c>
       <c r="F50" t="n">
-        <v>18.32</v>
+        <v>3.18</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>[6294.88, 7050.63, 7755.48]</t>
+          <t>[6496.87, 6790.22, 6083.47]</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>[5613.89, 6157.31, 6043.79]</t>
+          <t>[6486.09, 6221.83, 6069.31]</t>
         </is>
       </c>
     </row>
@@ -2262,31 +2262,31 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1720.32</v>
+        <v>319.31</v>
       </c>
       <c r="E51" t="n">
-        <v>1598.41</v>
+        <v>246.14</v>
       </c>
       <c r="F51" t="n">
-        <v>26.46</v>
+        <v>3.97</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>[6966.13, 7663.78, 8364.6]</t>
+          <t>[6741.66, 6036.71, 6000.69]</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>[6157.31, 6043.79, 5998.19]</t>
+          <t>[6221.83, 6069.31, 6186.68]</t>
         </is>
       </c>
     </row>
@@ -2298,31 +2298,31 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="E52" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="F52" t="n">
         <v>100</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>[0.0, -0.0, -0.0]</t>
+          <t>[0.0, -0.0, 0.0]</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>[0.2, 0.1, 0.1]</t>
+          <t>[0.1, 0.1, 0.1]</t>
         </is>
       </c>
     </row>
@@ -2334,12 +2334,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2349,11 +2349,11 @@
         <v>0.1</v>
       </c>
       <c r="F53" t="n">
-        <v>100</v>
+        <v>99.97</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>[-0.0, 0.0, -0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2385,11 +2385,11 @@
         <v>0.1</v>
       </c>
       <c r="F54" t="n">
-        <v>100</v>
+        <v>99.97</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>[0.0, -0.0, -0.0]</t>
+          <t>[0.0, 0.0, -0.0]</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2421,7 +2421,7 @@
         <v>0.1</v>
       </c>
       <c r="F55" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2457,11 +2457,11 @@
         <v>0.1</v>
       </c>
       <c r="F56" t="n">
-        <v>100</v>
+        <v>99.98</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>[-0.0, 0.0, -0.0]</t>
+          <t>[-0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2478,12 +2478,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2493,11 +2493,11 @@
         <v>0.1</v>
       </c>
       <c r="F57" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>[0.0, -0.0, -0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2514,12 +2514,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2529,11 +2529,11 @@
         <v>0.1</v>
       </c>
       <c r="F58" t="n">
-        <v>100</v>
+        <v>99.97</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, -0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2550,12 +2550,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2565,11 +2565,11 @@
         <v>0.1</v>
       </c>
       <c r="F59" t="n">
-        <v>100</v>
+        <v>99.95999999999999</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>[0.0, -0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2601,7 +2601,7 @@
         <v>0.1</v>
       </c>
       <c r="F60" t="n">
-        <v>99.97</v>
+        <v>99.94</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2622,12 +2622,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2637,11 +2637,11 @@
         <v>0.1</v>
       </c>
       <c r="F61" t="n">
-        <v>99.97</v>
+        <v>99.95</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, -0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2658,12 +2658,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, -0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2696,12 +2696,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, -0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2734,19 +2734,19 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -2755,12 +2755,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.1]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -2772,19 +2772,19 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>[-0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, -0.0]</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>[0.0, 0.1, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -2810,19 +2810,19 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -2831,12 +2831,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, -0.0]</t>
+          <t>[0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>[0.1, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -2848,12 +2848,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>[0.0, -0.0, 0.0]</t>
+          <t>[-0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -2886,12 +2886,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>[-0.0, 0.0, 0.0]</t>
+          <t>[-0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[-0.0, -0.0, 0.0]</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[-0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3000,12 +3000,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, -0.0]</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3038,31 +3038,31 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>191.26</v>
+        <v>37.57</v>
       </c>
       <c r="E72" t="n">
-        <v>127.15</v>
+        <v>35.17</v>
       </c>
       <c r="F72" t="n">
-        <v>1868.24</v>
+        <v>879</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>[27.31, 335.68, 92.76]</t>
+          <t>[37.25, 56.23, 24.52]</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>[4.6, 6.5, 63.19]</t>
+          <t>[3.3, 4.3, 4.9]</t>
         </is>
       </c>
     </row>
@@ -3074,31 +3074,31 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>198.69</v>
+        <v>46.37</v>
       </c>
       <c r="E73" t="n">
-        <v>135.47</v>
+        <v>43.46</v>
       </c>
       <c r="F73" t="n">
-        <v>1766.94</v>
+        <v>901.33</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>[346.6, 79.53, 67.13]</t>
+          <t>[60.96, 25.59, 58.53]</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>[6.5, 63.19, 117.1]</t>
+          <t>[4.3, 4.9, 5.5]</t>
         </is>
       </c>
     </row>
@@ -3110,31 +3110,31 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>64.73999999999999</v>
+        <v>36.89</v>
       </c>
       <c r="E74" t="n">
-        <v>56.68</v>
+        <v>33.29</v>
       </c>
       <c r="F74" t="n">
-        <v>849.76</v>
+        <v>519.53</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>[49.74, 46.89, 89.88]</t>
+          <t>[28.19, 61.22, 50.57]</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>[63.19, 117.1, 3.5]</t>
+          <t>[4.9, 5.5, 29.7]</t>
         </is>
       </c>
     </row>
@@ -3146,31 +3146,31 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>70.56</v>
+        <v>42.19</v>
       </c>
       <c r="E75" t="n">
-        <v>69.12</v>
+        <v>39.17</v>
       </c>
       <c r="F75" t="n">
-        <v>1229.17</v>
+        <v>693.46</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>[46.16, 89.0, 55.22]</t>
+          <t>[65.79, 52.42, 38.3]</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>[117.1, 3.5, 4.3]</t>
+          <t>[5.5, 29.7, 3.8]</t>
         </is>
       </c>
     </row>
@@ -3182,31 +3182,31 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>58.26</v>
+        <v>32.57</v>
       </c>
       <c r="E76" t="n">
-        <v>53.99</v>
+        <v>32.42</v>
       </c>
       <c r="F76" t="n">
-        <v>1187.53</v>
+        <v>554.46</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>[86.02, 54.47, 47.42]</t>
+          <t>[58.17, 40.01, 37.87]</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>[3.5, 4.3, 76.7]</t>
+          <t>[29.7, 3.8, 5.3]</t>
         </is>
       </c>
     </row>
@@ -3218,31 +3218,31 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>40.81</v>
+        <v>33.4</v>
       </c>
       <c r="E77" t="n">
-        <v>38.88</v>
+        <v>33.24</v>
       </c>
       <c r="F77" t="n">
-        <v>784.33</v>
+        <v>897.89</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>[60.31, 49.55, 36.8]</t>
+          <t>[41.06, 38.36, 32.11]</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>[4.3, 76.7, 3.3]</t>
+          <t>[3.8, 5.3, 2.7]</t>
         </is>
       </c>
     </row>
@@ -3254,31 +3254,31 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>38.64</v>
+        <v>38.05</v>
       </c>
       <c r="E78" t="n">
-        <v>36.66</v>
+        <v>37.3</v>
       </c>
       <c r="F78" t="n">
-        <v>766.42</v>
+        <v>903.55</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>[53.82, 37.86, 56.85]</t>
+          <t>[42.88, 30.66, 51.16]</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>[76.7, 3.3, 4.3]</t>
+          <t>[5.3, 2.7, 4.8]</t>
         </is>
       </c>
     </row>
@@ -3290,31 +3290,31 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>37.57</v>
+        <v>30.18</v>
       </c>
       <c r="E79" t="n">
-        <v>35.17</v>
+        <v>26.78</v>
       </c>
       <c r="F79" t="n">
-        <v>879</v>
+        <v>725.95</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>[37.25, 56.23, 24.52]</t>
+          <t>[29.67, 48.53, 13.25]</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>[3.3, 4.3, 4.9]</t>
+          <t>[2.7, 4.8, 3.6]</t>
         </is>
       </c>
     </row>
@@ -3326,31 +3326,31 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>46.37</v>
+        <v>24.36</v>
       </c>
       <c r="E80" t="n">
-        <v>43.46</v>
+        <v>18.47</v>
       </c>
       <c r="F80" t="n">
-        <v>901.33</v>
+        <v>409.86</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>[60.96, 25.59, 58.53]</t>
+          <t>[45.67, 12.42, 10.03]</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>[4.3, 4.9, 5.5]</t>
+          <t>[4.8, 3.6, 4.3]</t>
         </is>
       </c>
     </row>
@@ -3362,31 +3362,31 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>36.89</v>
+        <v>10.76</v>
       </c>
       <c r="E81" t="n">
-        <v>33.29</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F81" t="n">
-        <v>519.53</v>
+        <v>247.14</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>[28.19, 61.22, 50.57]</t>
+          <t>[11.66, 9.31, 20.04]</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>[4.9, 5.5, 29.7]</t>
+          <t>[3.6, 4.3, 4.0]</t>
         </is>
       </c>
     </row>
@@ -3398,31 +3398,31 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>299.47</v>
+        <v>402.2</v>
       </c>
       <c r="E82" t="n">
-        <v>257.99</v>
+        <v>356.47</v>
       </c>
       <c r="F82" t="n">
-        <v>16.64</v>
+        <v>19.63</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>[1429.82, 1156.91, 1153.46]</t>
+          <t>[1419.11, 2436.23, 1819.33]</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>[1595.03, 1629.31, 1289.81]</t>
+          <t>[1658.56, 1816.86, 2029.92]</t>
         </is>
       </c>
     </row>
@@ -3434,31 +3434,31 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>280.05</v>
+        <v>466.06</v>
       </c>
       <c r="E83" t="n">
-        <v>235.13</v>
+        <v>385.73</v>
       </c>
       <c r="F83" t="n">
-        <v>14.78</v>
+        <v>20.82</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>[1179.07, 1159.99, 1763.2]</t>
+          <t>[2566.81, 1882.4, 2125.26]</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>[1629.31, 1289.81, 1888.54]</t>
+          <t>[1816.86, 2029.92, 1865.53]</t>
         </is>
       </c>
     </row>
@@ -3470,31 +3470,31 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>350.74</v>
+        <v>507.73</v>
       </c>
       <c r="E84" t="n">
-        <v>232.51</v>
+        <v>410.64</v>
       </c>
       <c r="F84" t="n">
-        <v>13.95</v>
+        <v>19.73</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>[1225.76, 1858.42, 2312.5]</t>
+          <t>[1879.61, 2118.38, 2995.79]</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>[1289.81, 1888.54, 1709.14]</t>
+          <t>[2029.92, 1865.53, 2167.03]</t>
         </is>
       </c>
     </row>
@@ -3506,31 +3506,31 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>544.38</v>
+        <v>584.1799999999999</v>
       </c>
       <c r="E85" t="n">
-        <v>449.77</v>
+        <v>532.29</v>
       </c>
       <c r="F85" t="n">
-        <v>27.7</v>
+        <v>25.91</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>[1862.32, 2289.82, 2297.52]</t>
+          <t>[2135.94, 3018.57, 1508.75]</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>[1888.54, 1709.14, 1555.1]</t>
+          <t>[1865.53, 2167.03, 1983.67]</t>
         </is>
       </c>
     </row>
@@ -3542,31 +3542,31 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>618.12</v>
+        <v>921.12</v>
       </c>
       <c r="E86" t="n">
-        <v>614.1900000000001</v>
+        <v>874.17</v>
       </c>
       <c r="F86" t="n">
-        <v>38.39</v>
+        <v>44.95</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>[2257.58, 2265.66, 2144.62]</t>
+          <t>[2919.29, 1388.09, 3092.31]</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>[1709.14, 1555.1, 1561.05]</t>
+          <t>[2167.03, 1983.67, 1817.65]</t>
         </is>
       </c>
     </row>
@@ -3578,31 +3578,31 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>539.5599999999999</v>
+        <v>831.65</v>
       </c>
       <c r="E87" t="n">
-        <v>497.34</v>
+        <v>800.74</v>
       </c>
       <c r="F87" t="n">
-        <v>31.66</v>
+        <v>37.73</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>[2243.52, 2158.52, 1452.42]</t>
+          <t>[1493.62, 2716.39, 1582.65]</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>[1555.1, 1561.05, 1658.56]</t>
+          <t>[1983.67, 1817.65, 2596.07]</t>
         </is>
       </c>
     </row>
@@ -3614,31 +3614,31 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>510.63</v>
+        <v>827.41</v>
       </c>
       <c r="E88" t="n">
-        <v>475.67</v>
+        <v>786.5700000000001</v>
       </c>
       <c r="F88" t="n">
-        <v>28.24</v>
+        <v>37.19</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>[2117.95, 1439.78, 2468.19]</t>
+          <t>[2753.64, 1597.66, 2393.61]</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>[1561.05, 1658.56, 1816.86]</t>
+          <t>[1817.65, 2596.07, 1968.29]</t>
         </is>
       </c>
     </row>
@@ -3650,31 +3650,31 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>402.2</v>
+        <v>765.5</v>
       </c>
       <c r="E89" t="n">
-        <v>356.47</v>
+        <v>715.02</v>
       </c>
       <c r="F89" t="n">
-        <v>19.63</v>
+        <v>32.28</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>[1419.11, 2436.23, 1819.33]</t>
+          <t>[1561.54, 2335.03, 2683.43]</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>[1658.56, 1816.86, 2029.92]</t>
+          <t>[2596.07, 1968.29, 1939.64]</t>
         </is>
       </c>
     </row>
@@ -3686,31 +3686,31 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>466.06</v>
+        <v>827.01</v>
       </c>
       <c r="E90" t="n">
-        <v>385.73</v>
+        <v>779.29</v>
       </c>
       <c r="F90" t="n">
-        <v>20.82</v>
+        <v>43.64</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>[2566.81, 1882.4, 2125.26]</t>
+          <t>[2392.88, 2752.63, 2732.24]</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>[1816.86, 2029.92, 1865.53]</t>
+          <t>[1968.29, 1939.64, 1631.96]</t>
         </is>
       </c>
     </row>
@@ -3722,31 +3722,31 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>507.73</v>
+        <v>810.51</v>
       </c>
       <c r="E91" t="n">
-        <v>410.64</v>
+        <v>790.04</v>
       </c>
       <c r="F91" t="n">
-        <v>19.73</v>
+        <v>45.12</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>[1879.61, 2118.38, 2995.79]</t>
+          <t>[2685.16, 2662.59, 2353.43]</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>[2029.92, 1865.53, 2167.03]</t>
+          <t>[1939.64, 1631.96, 1759.46]</t>
         </is>
       </c>
     </row>
@@ -3758,31 +3758,31 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>437.29</v>
+        <v>156.02</v>
       </c>
       <c r="E92" t="n">
-        <v>424.16</v>
+        <v>149.5</v>
       </c>
       <c r="F92" t="n">
-        <v>43.54</v>
+        <v>14.89</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>[1679.61, 1332.46, 1145.45]</t>
+          <t>[1157.13, 1172.48, 1174.21]</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>[1106.81, 962.8, 815.43]</t>
+          <t>[1035.3, 960.03, 1059.99]</t>
         </is>
       </c>
     </row>
@@ -3794,31 +3794,31 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>252.12</v>
+        <v>158.07</v>
       </c>
       <c r="E93" t="n">
-        <v>237.27</v>
+        <v>153.27</v>
       </c>
       <c r="F93" t="n">
-        <v>25.61</v>
+        <v>14.59</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>[1280.72, 1089.97, 1295.82]</t>
+          <t>[1167.85, 1183.34, 1354.89]</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>[962.8, 815.43, 1176.48]</t>
+          <t>[960.03, 1059.99, 1226.25]</t>
         </is>
       </c>
     </row>
@@ -3830,31 +3830,31 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>173.74</v>
+        <v>494.56</v>
       </c>
       <c r="E94" t="n">
-        <v>163.5</v>
+        <v>357.29</v>
       </c>
       <c r="F94" t="n">
-        <v>17.08</v>
+        <v>35.03</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>[1057.41, 1277.05, 1283.8]</t>
+          <t>[1169.32, 1347.97, 1831.87]</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>[815.43, 1176.48, 1135.85]</t>
+          <t>[1059.99, 1226.25, 991.03]</t>
         </is>
       </c>
     </row>
@@ -3866,31 +3866,31 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>505.82</v>
+        <v>627.12</v>
       </c>
       <c r="E95" t="n">
-        <v>365.43</v>
+        <v>550.17</v>
       </c>
       <c r="F95" t="n">
-        <v>38.6</v>
+        <v>54.83</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>[1270.82, 1278.57, 1761.76]</t>
+          <t>[1390.56, 1889.8, 1560.06]</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>[1176.48, 1135.85, 902.53]</t>
+          <t>[1226.25, 991.03, 972.64]</t>
         </is>
       </c>
     </row>
@@ -3902,31 +3902,31 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>507.85</v>
+        <v>632.72</v>
       </c>
       <c r="E96" t="n">
-        <v>346.21</v>
+        <v>608.65</v>
       </c>
       <c r="F96" t="n">
-        <v>37.05</v>
+        <v>60.97</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>[1292.18, 1767.98, 1115.96]</t>
+          <t>[1835.43, 1519.31, 1482.77]</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>[1135.85, 902.53, 1132.8]</t>
+          <t>[991.03, 972.64, 1047.88]</t>
         </is>
       </c>
     </row>
@@ -3938,31 +3938,31 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>527.59</v>
+        <v>356.34</v>
       </c>
       <c r="E97" t="n">
-        <v>370.15</v>
+        <v>323.23</v>
       </c>
       <c r="F97" t="n">
-        <v>39.94</v>
+        <v>31.6</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>[1791.13, 1123.93, 1248.3]</t>
+          <t>[1463.39, 1400.07, 1052.42]</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>[902.53, 1132.8, 1035.3]</t>
+          <t>[972.64, 1047.88, 1179.17]</t>
         </is>
       </c>
     </row>
@@ -3974,31 +3974,31 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>140.49</v>
+        <v>259.34</v>
       </c>
       <c r="E98" t="n">
-        <v>133.49</v>
+        <v>243.4</v>
       </c>
       <c r="F98" t="n">
-        <v>13.1</v>
+        <v>23.09</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>[1030.12, 1137.71, 1155.42]</t>
+          <t>[1413.05, 1026.68, 1201.78]</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>[1132.8, 1035.3, 960.03]</t>
+          <t>[1047.88, 1179.17, 989.24]</t>
         </is>
       </c>
     </row>
@@ -4010,31 +4010,31 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>156.02</v>
+        <v>151.65</v>
       </c>
       <c r="E99" t="n">
-        <v>149.5</v>
+        <v>144.64</v>
       </c>
       <c r="F99" t="n">
-        <v>14.89</v>
+        <v>13.33</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>[1157.13, 1172.48, 1174.21]</t>
+          <t>[993.31, 1156.2, 1183.03]</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>[1035.3, 960.03, 1059.99]</t>
+          <t>[1179.17, 989.24, 1101.94]</t>
         </is>
       </c>
     </row>
@@ -4046,31 +4046,31 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>158.07</v>
+        <v>321.44</v>
       </c>
       <c r="E100" t="n">
-        <v>153.27</v>
+        <v>280.22</v>
       </c>
       <c r="F100" t="n">
-        <v>14.59</v>
+        <v>27.56</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>[1167.85, 1183.34, 1354.89]</t>
+          <t>[1203.12, 1231.22, 1506.06]</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>[960.03, 1059.99, 1226.25]</t>
+          <t>[989.24, 1101.94, 1008.55]</t>
         </is>
       </c>
     </row>
@@ -4082,31 +4082,31 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>494.56</v>
+        <v>288.74</v>
       </c>
       <c r="E101" t="n">
-        <v>357.29</v>
+        <v>236.35</v>
       </c>
       <c r="F101" t="n">
-        <v>35.03</v>
+        <v>23.61</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>[1169.32, 1347.97, 1831.87]</t>
+          <t>[1205.9, 1478.79, 1047.8]</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>[1059.99, 1226.25, 991.03]</t>
+          <t>[1101.94, 1008.55, 912.93]</t>
         </is>
       </c>
     </row>
@@ -4118,31 +4118,31 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>179.59</v>
+        <v>163.62</v>
       </c>
       <c r="E102" t="n">
-        <v>159.62</v>
+        <v>131.86</v>
       </c>
       <c r="F102" t="n">
-        <v>15.65</v>
+        <v>12.31</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>[830.89, 732.82, 904.39]</t>
+          <t>[830.53, 1043.47, 895.37]</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>[882.31, 909.42, 1155.23]</t>
+          <t>[977.18, 1036.95, 1137.79]</t>
         </is>
       </c>
     </row>
@@ -4154,31 +4154,31 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>179.66</v>
+        <v>136.27</v>
       </c>
       <c r="E103" t="n">
-        <v>165.5</v>
+        <v>96.27</v>
       </c>
       <c r="F103" t="n">
-        <v>16.08</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>[737.55, 907.47, 895.53]</t>
+          <t>[1050.96, 906.18, 890.93]</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>[909.42, 1155.23, 972.4]</t>
+          <t>[1036.95, 1137.79, 934.12]</t>
         </is>
       </c>
     </row>
@@ -4190,31 +4190,31 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>224.97</v>
+        <v>134.37</v>
       </c>
       <c r="E104" t="n">
-        <v>197.81</v>
+        <v>103.22</v>
       </c>
       <c r="F104" t="n">
-        <v>18.48</v>
+        <v>9.31</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>[932.36, 916.55, 720.15]</t>
+          <t>[913.09, 897.49, 1180.56]</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>[1155.23, 972.4, 1034.85]</t>
+          <t>[1137.79, 934.12, 1132.22]</t>
         </is>
       </c>
     </row>
@@ -4226,31 +4226,31 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>180.4</v>
+        <v>98.31999999999999</v>
       </c>
       <c r="E105" t="n">
-        <v>135.21</v>
+        <v>82.48</v>
       </c>
       <c r="F105" t="n">
-        <v>13.42</v>
+        <v>7.95</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>[921.01, 730.76, 844.54]</t>
+          <t>[918.15, 1216.68, 853.83]</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>[972.4, 1034.85, 894.67]</t>
+          <t>[934.12, 1132.22, 1000.83]</t>
         </is>
       </c>
     </row>
@@ -4262,31 +4262,31 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>175.79</v>
+        <v>97.81</v>
       </c>
       <c r="E106" t="n">
-        <v>122.19</v>
+        <v>84.86</v>
       </c>
       <c r="F106" t="n">
-        <v>12.18</v>
+        <v>8.23</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>[734.3, 851.84, 836.23]</t>
+          <t>[1221.34, 858.63, 915.36]</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>[1034.85, 894.67, 859.41]</t>
+          <t>[1132.22, 1000.83, 892.11]</t>
         </is>
       </c>
     </row>
@@ -4298,31 +4298,31 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>90.76000000000001</v>
+        <v>158.54</v>
       </c>
       <c r="E107" t="n">
-        <v>58.94</v>
+        <v>133.73</v>
       </c>
       <c r="F107" t="n">
-        <v>6.11</v>
+        <v>14.56</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>[882.11, 867.16, 820.67]</t>
+          <t>[860.39, 918.37, 1112.23]</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>[894.67, 859.41, 977.18]</t>
+          <t>[1000.83, 892.11, 877.74]</t>
         </is>
       </c>
     </row>
@@ -4334,31 +4334,31 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>87.83</v>
+        <v>147.3</v>
       </c>
       <c r="E108" t="n">
-        <v>56.3</v>
+        <v>106.46</v>
       </c>
       <c r="F108" t="n">
-        <v>5.83</v>
+        <v>11.9</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>[874.37, 825.81, 1034.38]</t>
+          <t>[927.97, 1128.16, 1079.91]</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>[859.41, 977.18, 1036.95]</t>
+          <t>[892.11, 877.74, 1046.8]</t>
         </is>
       </c>
     </row>
@@ -4370,31 +4370,31 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>163.62</v>
+        <v>149.22</v>
       </c>
       <c r="E109" t="n">
-        <v>131.86</v>
+        <v>108.93</v>
       </c>
       <c r="F109" t="n">
-        <v>12.31</v>
+        <v>12.13</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>[830.53, 1043.47, 895.37]</t>
+          <t>[1130.89, 1082.34, 958.22]</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>[977.18, 1036.95, 1137.79]</t>
+          <t>[877.74, 1046.8, 920.13]</t>
         </is>
       </c>
     </row>
@@ -4406,31 +4406,31 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>136.27</v>
+        <v>31.47</v>
       </c>
       <c r="E110" t="n">
-        <v>96.27</v>
+        <v>21.68</v>
       </c>
       <c r="F110" t="n">
-        <v>8.779999999999999</v>
+        <v>2.04</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>[1050.96, 906.18, 890.93]</t>
+          <t>[1049.71, 928.47, 1037.1]</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>[1036.95, 1137.79, 934.12]</t>
+          <t>[1046.8, 920.13, 1090.89]</t>
         </is>
       </c>
     </row>
@@ -4442,31 +4442,31 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>134.37</v>
+        <v>85.87</v>
       </c>
       <c r="E111" t="n">
-        <v>103.22</v>
+        <v>67.3</v>
       </c>
       <c r="F111" t="n">
-        <v>9.31</v>
+        <v>7.35</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>[913.09, 897.49, 1180.56]</t>
+          <t>[933.6, 1042.46, 1006.55]</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>[1137.79, 934.12, 1132.22]</t>
+          <t>[920.13, 1090.89, 866.57]</t>
         </is>
       </c>
     </row>
@@ -4478,31 +4478,31 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>249.04</v>
+        <v>348.16</v>
       </c>
       <c r="E112" t="n">
-        <v>219.87</v>
+        <v>276.85</v>
       </c>
       <c r="F112" t="n">
-        <v>18.94</v>
+        <v>20.03</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>[1430.36, 1405.19, 1477.09]</t>
+          <t>[913.04, 1000.39, 1218.37]</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>[1358.71, 1174.79, 1119.53]</t>
+          <t>[1466.16, 1237.16, 1259.01]</t>
         </is>
       </c>
     </row>
@@ -4514,31 +4514,31 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>266.73</v>
+        <v>107.96</v>
       </c>
       <c r="E113" t="n">
-        <v>253.26</v>
+        <v>81.47</v>
       </c>
       <c r="F113" t="n">
-        <v>22.32</v>
+        <v>6.55</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>[1413.09, 1481.97, 1271.88]</t>
+          <t>[1056.63, 1277.98, 1224.78]</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>[1174.79, 1119.53, 1112.85]</t>
+          <t>[1237.16, 1259.01, 1269.69]</t>
         </is>
       </c>
     </row>
@@ -4550,31 +4550,31 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>206.06</v>
+        <v>445.85</v>
       </c>
       <c r="E114" t="n">
-        <v>179.97</v>
+        <v>277.11</v>
       </c>
       <c r="F114" t="n">
-        <v>16.33</v>
+        <v>18.28</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>[1441.09, 1230.38, 1140.39]</t>
+          <t>[1296.06, 1246.41, 2310.94]</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>[1119.53, 1112.85, 1039.56]</t>
+          <t>[1259.01, 1269.69, 1539.94]</t>
         </is>
       </c>
     </row>
@@ -4586,31 +4586,31 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>447.22</v>
+        <v>461.78</v>
       </c>
       <c r="E115" t="n">
-        <v>321.38</v>
+        <v>344.07</v>
       </c>
       <c r="F115" t="n">
-        <v>47.49</v>
+        <v>22.63</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>[1223.58, 1131.88, 1376.66]</t>
+          <t>[1256.81, 2294.6, 1216.92]</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>[1112.85, 1039.56, 615.58]</t>
+          <t>[1269.69, 1539.94, 1481.59]</t>
         </is>
       </c>
     </row>
@@ -4622,31 +4622,31 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>553.21</v>
+        <v>473.47</v>
       </c>
       <c r="E116" t="n">
-        <v>472.62</v>
+        <v>395.67</v>
       </c>
       <c r="F116" t="n">
-        <v>79.48999999999999</v>
+        <v>26.32</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>[1110.46, 1343.58, 1164.82]</t>
+          <t>[2295.62, 1200.93, 1227.16]</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>[1039.56, 615.58, 545.87]</t>
+          <t>[1539.94, 1481.59, 1377.83]</t>
         </is>
       </c>
     </row>
@@ -4658,31 +4658,31 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>597.78</v>
+        <v>274</v>
       </c>
       <c r="E117" t="n">
-        <v>582.2</v>
+        <v>268.87</v>
       </c>
       <c r="F117" t="n">
-        <v>86.2</v>
+        <v>18.7</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>[1344.94, 1160.97, 1064.02]</t>
+          <t>[1138.48, 1152.55, 1197.75]</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>[615.58, 545.87, 1466.16]</t>
+          <t>[1481.59, 1377.83, 1435.98]</t>
         </is>
       </c>
     </row>
@@ -4694,31 +4694,31 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>433.1</v>
+        <v>158.65</v>
       </c>
       <c r="E118" t="n">
-        <v>401.96</v>
+        <v>139.66</v>
       </c>
       <c r="F118" t="n">
-        <v>48.49</v>
+        <v>10.13</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>[1076.62, 965.6, 1062.58]</t>
+          <t>[1191.35, 1236.94, 1145.42]</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>[545.87, 1466.16, 1237.16]</t>
+          <t>[1377.83, 1435.98, 1111.97]</t>
         </is>
       </c>
     </row>
@@ -4730,31 +4730,31 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>348.16</v>
+        <v>114.25</v>
       </c>
       <c r="E119" t="n">
-        <v>276.85</v>
+        <v>105.26</v>
       </c>
       <c r="F119" t="n">
-        <v>20.03</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>[913.04, 1000.39, 1218.37]</t>
+          <t>[1269.21, 1175.45, 1148.44]</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>[1466.16, 1237.16, 1259.01]</t>
+          <t>[1435.98, 1111.97, 1062.91]</t>
         </is>
       </c>
     </row>
@@ -4766,31 +4766,31 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>107.96</v>
+        <v>103.53</v>
       </c>
       <c r="E120" t="n">
-        <v>81.47</v>
+        <v>97.12</v>
       </c>
       <c r="F120" t="n">
-        <v>6.55</v>
+        <v>9.4</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>[1056.63, 1277.98, 1224.78]</t>
+          <t>[1174.1, 1145.76, 1135.16]</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>[1237.16, 1259.01, 1269.69]</t>
+          <t>[1111.97, 1062.91, 988.78]</t>
         </is>
       </c>
     </row>
@@ -4802,31 +4802,31 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>445.85</v>
+        <v>125.27</v>
       </c>
       <c r="E121" t="n">
-        <v>277.11</v>
+        <v>122.26</v>
       </c>
       <c r="F121" t="n">
-        <v>18.28</v>
+        <v>11.77</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>[1296.06, 1246.41, 2310.94]</t>
+          <t>[1147.65, 1137.67, 950.04]</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>[1259.01, 1269.69, 1539.94]</t>
+          <t>[1062.91, 988.78, 1083.18]</t>
         </is>
       </c>
     </row>
@@ -4838,31 +4838,31 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1.78</v>
+        <v>15.41</v>
       </c>
       <c r="E122" t="n">
-        <v>1.71</v>
+        <v>11.76</v>
       </c>
       <c r="F122" t="n">
-        <v>91.23</v>
+        <v>219.65</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>[0.05, 2.28, 2.47]</t>
+          <t>[4.66, 5.65, 8.15]</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>[1.5, 1.0, 4.88]</t>
+          <t>[1.2, 31.41, 2.1]</t>
         </is>
       </c>
     </row>
@@ -4874,31 +4874,31 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1.72</v>
+        <v>16.24</v>
       </c>
       <c r="E123" t="n">
-        <v>1.72</v>
+        <v>13.44</v>
       </c>
       <c r="F123" t="n">
-        <v>77.45</v>
+        <v>293.82</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>[2.56, 3.16, 2.66]</t>
+          <t>[5.18, 7.7, 10.1]</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>[1.0, 4.88, 4.53]</t>
+          <t>[31.41, 2.1, 1.6]</t>
         </is>
       </c>
     </row>
@@ -4910,31 +4910,31 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>4.41</v>
+        <v>12.62</v>
       </c>
       <c r="E124" t="n">
-        <v>3.63</v>
+        <v>11.19</v>
       </c>
       <c r="F124" t="n">
-        <v>49.84</v>
+        <v>286.76</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>[3.08, 2.59, 3.1]</t>
+          <t>[7.67, 10.37, 21.82]</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>[4.88, 4.53, 10.26]</t>
+          <t>[2.1, 1.6, 41.06]</t>
         </is>
       </c>
     </row>
@@ -4946,31 +4946,31 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>4.45</v>
+        <v>11.71</v>
       </c>
       <c r="E125" t="n">
-        <v>3.88</v>
+        <v>9.23</v>
       </c>
       <c r="F125" t="n">
-        <v>162.45</v>
+        <v>211.7</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>[2.82, 3.4, 3.86]</t>
+          <t>[10.2, 22.71, 0.66]</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>[4.53, 10.26, 0.8]</t>
+          <t>[1.6, 41.06, 1.4]</t>
         </is>
       </c>
     </row>
@@ -4982,31 +4982,31 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>8.359999999999999</v>
+        <v>12.25</v>
       </c>
       <c r="E126" t="n">
-        <v>7.37</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="F126" t="n">
-        <v>153.14</v>
+        <v>60.84</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>[2.96, 3.36, 5.58]</t>
+          <t>[21.72, 0.62, 2.25]</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>[10.26, 0.8, 17.82]</t>
+          <t>[41.06, 1.4, 10.95]</t>
         </is>
       </c>
     </row>
@@ -5018,31 +5018,31 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>7.16</v>
+        <v>5.03</v>
       </c>
       <c r="E127" t="n">
-        <v>5.93</v>
+        <v>3.32</v>
       </c>
       <c r="F127" t="n">
-        <v>235</v>
+        <v>44.87</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>[3.73, 6.23, 4.48]</t>
+          <t>[0.8, 2.29, 4.61]</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>[0.8, 17.82, 1.2]</t>
+          <t>[1.4, 10.95, 5.3]</t>
         </is>
       </c>
     </row>
@@ -5054,31 +5054,31 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>16.56</v>
+        <v>5.14</v>
       </c>
       <c r="E128" t="n">
-        <v>13.62</v>
+        <v>3.73</v>
       </c>
       <c r="F128" t="n">
-        <v>139.58</v>
+        <v>41.69</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>[6.29, 4.45, 5.34]</t>
+          <t>[2.29, 4.75, 3.61]</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>[17.82, 1.2, 31.41]</t>
+          <t>[10.95, 5.3, 5.6]</t>
         </is>
       </c>
     </row>
@@ -5090,31 +5090,31 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>15.41</v>
+        <v>1.18</v>
       </c>
       <c r="E129" t="n">
-        <v>11.76</v>
+        <v>1.01</v>
       </c>
       <c r="F129" t="n">
-        <v>219.65</v>
+        <v>22.47</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>[4.66, 5.65, 8.15]</t>
+          <t>[5.11, 3.98, 4.72]</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>[1.2, 31.41, 2.1]</t>
+          <t>[5.3, 5.6, 3.5]</t>
         </is>
       </c>
     </row>
@@ -5126,31 +5126,31 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>16.24</v>
+        <v>2.78</v>
       </c>
       <c r="E130" t="n">
-        <v>13.44</v>
+        <v>2.37</v>
       </c>
       <c r="F130" t="n">
-        <v>293.82</v>
+        <v>38.46</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>[5.18, 7.7, 10.1]</t>
+          <t>[3.85, 4.51, 3.54]</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>[31.41, 2.1, 1.6]</t>
+          <t>[5.6, 3.5, 7.9]</t>
         </is>
       </c>
     </row>
@@ -5162,31 +5162,31 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>12.62</v>
+        <v>5.16</v>
       </c>
       <c r="E131" t="n">
-        <v>11.19</v>
+        <v>4.37</v>
       </c>
       <c r="F131" t="n">
-        <v>286.76</v>
+        <v>886.6</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>[7.67, 10.37, 21.82]</t>
+          <t>[4.49, 3.51, 8.03]</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>[2.1, 1.6, 41.06]</t>
+          <t>[3.5, 7.9, 0.3]</t>
         </is>
       </c>
     </row>
@@ -5198,31 +5198,31 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>32913.38</v>
+        <v>380645.1</v>
       </c>
       <c r="E132" t="n">
-        <v>28802.43</v>
+        <v>222628.58</v>
       </c>
       <c r="F132" t="n">
-        <v>4008.19</v>
+        <v>58267.5</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>[51848.29, 15649.72, 21069.82]</t>
+          <t>[6191.04, 659646.69, 3951.08]</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>[719.0, 599.01, 842.52]</t>
+          <t>[921.96, 379.6, 601.52]</t>
         </is>
       </c>
     </row>
@@ -5234,31 +5234,31 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>5821.03</v>
+        <v>346213.26</v>
       </c>
       <c r="E133" t="n">
-        <v>5109.59</v>
+        <v>212963.51</v>
       </c>
       <c r="F133" t="n">
-        <v>696.4</v>
+        <v>54264.58</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>[6246.58, 9066.57, 2312.99]</t>
+          <t>[598869.56, 3705.93, 38104.43]</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>[599.01, 842.52, 855.84]</t>
+          <t>[379.6, 601.52, 808.27]</t>
         </is>
       </c>
     </row>
@@ -5270,31 +5270,31 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>24684.71</v>
+        <v>172765.29</v>
       </c>
       <c r="E134" t="n">
-        <v>18375.07</v>
+        <v>110501.37</v>
       </c>
       <c r="F134" t="n">
-        <v>2482.47</v>
+        <v>14586.57</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>[12514.94, 3247.22, 41771.51]</t>
+          <t>[3112.75, 32227.52, 298327.83]</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>[842.52, 855.84, 710.09]</t>
+          <t>[601.52, 808.27, 754.21]</t>
         </is>
       </c>
     </row>
@@ -5306,31 +5306,31 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>32348.03</v>
+        <v>189233</v>
       </c>
       <c r="E135" t="n">
-        <v>26929.17</v>
+        <v>158538.09</v>
       </c>
       <c r="F135" t="n">
-        <v>3943.46</v>
+        <v>24522.53</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>[3201.13, 45274.06, 34519.83]</t>
+          <t>[28285.88, 280765.09, 168634.6]</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>[855.84, 710.09, 641.57]</t>
+          <t>[808.27, 754.21, 508.83]</t>
         </is>
       </c>
     </row>
@@ -5342,31 +5342,31 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>21816.72</v>
+        <v>187768.91</v>
       </c>
       <c r="E136" t="n">
-        <v>17689.49</v>
+        <v>164349.83</v>
       </c>
       <c r="F136" t="n">
-        <v>2604.75</v>
+        <v>27107.26</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>[31042.18, 23176.7, 868.64]</t>
+          <t>[274246.22, 168900.13, 51593.79]</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>[710.09, 641.57, 667.37]</t>
+          <t>[754.21, 508.83, 427.6]</t>
         </is>
       </c>
     </row>
@@ -5378,31 +5378,31 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>12771.06</v>
+        <v>95914.69</v>
       </c>
       <c r="E137" t="n">
-        <v>9012.889999999999</v>
+        <v>84990.98</v>
       </c>
       <c r="F137" t="n">
-        <v>1319.85</v>
+        <v>16559.64</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>[22104.09, 894.82, 6270.65]</t>
+          <t>[147726.12, 46549.34, 62252.72]</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>[641.57, 667.37, 921.96]</t>
+          <t>[508.83, 427.6, 618.8]</t>
         </is>
       </c>
     </row>
@@ -5414,31 +5414,31 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>279539.79</v>
+        <v>42035.97</v>
       </c>
       <c r="E138" t="n">
-        <v>162757.02</v>
+        <v>38691.84</v>
       </c>
       <c r="F138" t="n">
-        <v>42664.65</v>
+        <v>6843.29</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>[745.26, 4954.81, 484539.92]</t>
+          <t>[40978.09, 58440.12, 18743.57]</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>[667.37, 921.96, 379.6]</t>
+          <t>[427.6, 618.8, 1039.88]</t>
         </is>
       </c>
     </row>
@@ -5450,31 +5450,31 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>380645.1</v>
+        <v>96525.42</v>
       </c>
       <c r="E139" t="n">
-        <v>222628.58</v>
+        <v>77514.58</v>
       </c>
       <c r="F139" t="n">
-        <v>58267.5</v>
+        <v>10854.18</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>[6191.04, 659646.69, 3951.08]</t>
+          <t>[59736.66, 19129.64, 156066.45]</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>[921.96, 379.6, 601.52]</t>
+          <t>[618.8, 1039.88, 730.33]</t>
         </is>
       </c>
     </row>
@@ -5486,31 +5486,31 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>346213.26</v>
+        <v>73980</v>
       </c>
       <c r="E140" t="n">
-        <v>212963.51</v>
+        <v>63663.22</v>
       </c>
       <c r="F140" t="n">
-        <v>54264.58</v>
+        <v>7949.43</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>[598869.56, 3705.93, 38104.43]</t>
+          <t>[12565.17, 100016.56, 81054.86]</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>[379.6, 601.52, 808.27]</t>
+          <t>[1039.88, 730.33, 876.72]</t>
         </is>
       </c>
     </row>
@@ -5522,31 +5522,31 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>172765.29</v>
+        <v>78292.45</v>
       </c>
       <c r="E141" t="n">
-        <v>110501.37</v>
+        <v>64920.94</v>
       </c>
       <c r="F141" t="n">
-        <v>14586.57</v>
+        <v>8200.09</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>[3112.75, 32227.52, 298327.83]</t>
+          <t>[105834.09, 86467.44, 4979.76]</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>[601.52, 808.27, 754.21]</t>
+          <t>[730.33, 876.72, 911.41]</t>
         </is>
       </c>
     </row>
@@ -5558,31 +5558,31 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>189.35</v>
+        <v>555.61</v>
       </c>
       <c r="E142" t="n">
-        <v>173.91</v>
+        <v>446.59</v>
       </c>
       <c r="F142" t="n">
-        <v>9.550000000000001</v>
+        <v>23.3</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>[2001.04, 2021.49, 2040.81]</t>
+          <t>[2820.68, 1491.11, 1864.2]</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>[1751.4, 1821.3, 2112.7]</t>
+          <t>[1936.9, 1862.4, 1948.9]</t>
         </is>
       </c>
     </row>
@@ -5594,31 +5594,31 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>164.32</v>
+        <v>457.75</v>
       </c>
       <c r="E143" t="n">
-        <v>147.33</v>
+        <v>437.35</v>
       </c>
       <c r="F143" t="n">
-        <v>7.23</v>
+        <v>22.52</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>[1880.01, 1875.74, 1871.18]</t>
+          <t>[1233.94, 1609.64, 1754.37]</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>[1821.3, 2112.7, 2017.5]</t>
+          <t>[1862.4, 1948.9, 2098.7]</t>
         </is>
       </c>
     </row>
@@ -5630,31 +5630,31 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>180</v>
+        <v>155.68</v>
       </c>
       <c r="E144" t="n">
-        <v>166.93</v>
+        <v>155.34</v>
       </c>
       <c r="F144" t="n">
-        <v>8.289999999999999</v>
+        <v>7.48</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>[1861.1, 1855.19, 1849.5]</t>
+          <t>[1779.15, 1949.27, 2079.15]</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>[2112.7, 2017.5, 1762.6]</t>
+          <t>[1948.9, 2098.7, 2226.0]</t>
         </is>
       </c>
     </row>
@@ -5666,31 +5666,31 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>169.08</v>
+        <v>117.71</v>
       </c>
       <c r="E145" t="n">
-        <v>159.28</v>
+        <v>116.07</v>
       </c>
       <c r="F145" t="n">
-        <v>8.93</v>
+        <v>5.59</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>[1934.34, 1937.96, 1941.71]</t>
+          <t>[1960.83, 2106.11, 1788.74]</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>[2017.5, 1762.6, 1722.4]</t>
+          <t>[2098.7, 2226.0, 1879.2]</t>
         </is>
       </c>
     </row>
@@ -5702,31 +5702,31 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>258.14</v>
+        <v>128.83</v>
       </c>
       <c r="E146" t="n">
-        <v>255.69</v>
+        <v>119.51</v>
       </c>
       <c r="F146" t="n">
-        <v>14.85</v>
+        <v>6.46</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>[1972.96, 1982.04, 1990.86]</t>
+          <t>[2122.91, 1808.64, 1498.62]</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>[1762.6, 1722.4, 1693.8]</t>
+          <t>[2226.0, 1879.2, 1683.5]</t>
         </is>
       </c>
     </row>
@@ -5738,31 +5738,31 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>157.28</v>
+        <v>197.31</v>
       </c>
       <c r="E147" t="n">
-        <v>140.4</v>
+        <v>173.3</v>
       </c>
       <c r="F147" t="n">
-        <v>8.130000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>[1898.83, 1897.21, 1895.54]</t>
+          <t>[1823.92, 1505.04, 2107.86]</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>[1722.4, 1693.8, 1936.9]</t>
+          <t>[1879.2, 1683.5, 1821.7]</t>
         </is>
       </c>
     </row>
@@ -5774,31 +5774,31 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>681.3</v>
+        <v>219.31</v>
       </c>
       <c r="E148" t="n">
-        <v>465.66</v>
+        <v>207.35</v>
       </c>
       <c r="F148" t="n">
-        <v>24.3</v>
+        <v>11.12</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>[1748.13, 3102.3, 1685.16]</t>
+          <t>[1518.07, 2129.6, 2091.07]</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>[1693.8, 1936.9, 1862.4]</t>
+          <t>[1683.5, 1821.7, 2239.8]</t>
         </is>
       </c>
     </row>
@@ -5810,31 +5810,31 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>555.61</v>
+        <v>237.86</v>
       </c>
       <c r="E149" t="n">
-        <v>446.59</v>
+        <v>186.69</v>
       </c>
       <c r="F149" t="n">
-        <v>23.3</v>
+        <v>9.68</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>[2820.68, 1491.11, 1864.2]</t>
+          <t>[2211.75, 2194.38, 2100.09]</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>[1936.9, 1862.4, 1948.9]</t>
+          <t>[1821.7, 2239.8, 2224.7]</t>
         </is>
       </c>
     </row>
@@ -5846,31 +5846,31 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>457.75</v>
+        <v>262.12</v>
       </c>
       <c r="E150" t="n">
-        <v>437.35</v>
+        <v>238.62</v>
       </c>
       <c r="F150" t="n">
-        <v>22.52</v>
+        <v>11.12</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>[1233.94, 1609.64, 1754.37]</t>
+          <t>[1977.43, 1866.71, 1816.2]</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>[1862.4, 1948.9, 2098.7]</t>
+          <t>[2239.8, 2224.7, 1720.7]</t>
         </is>
       </c>
     </row>
@@ -5882,31 +5882,31 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>155.68</v>
+        <v>210.16</v>
       </c>
       <c r="E151" t="n">
-        <v>155.34</v>
+        <v>205.03</v>
       </c>
       <c r="F151" t="n">
-        <v>7.48</v>
+        <v>10.28</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>[1779.15, 1949.27, 2079.15]</t>
+          <t>[1958.69, 1915.49, 1882.53]</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>[1948.9, 2098.7, 2226.0]</t>
+          <t>[2224.7, 1720.7, 2036.8]</t>
         </is>
       </c>
     </row>
@@ -5918,31 +5918,31 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>93.81999999999999</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="E152" t="n">
-        <v>73.73</v>
+        <v>7.87</v>
       </c>
       <c r="F152" t="n">
-        <v>82.27</v>
+        <v>66.09</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>[14.51, 13.59, 12.78]</t>
+          <t>[0.03, 0.16, 140.49]</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>[83.1, 160.8, 7.4]</t>
+          <t>[13.8, 9.8, 140.7]</t>
         </is>
       </c>
     </row>
@@ -5954,31 +5954,31 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>122.52</v>
+        <v>1446.16</v>
       </c>
       <c r="E153" t="n">
-        <v>103.45</v>
+        <v>863.58</v>
       </c>
       <c r="F153" t="n">
-        <v>109.22</v>
+        <v>1487.88</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>[19.19, 18.48, 17.74]</t>
+          <t>[0.05, 63.31, 2561.71]</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>[160.8, 7.4, 175.4]</t>
+          <t>[9.8, 140.7, 58.1]</t>
         </is>
       </c>
     </row>
@@ -5990,31 +5990,31 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>148.1</v>
+        <v>562.21</v>
       </c>
       <c r="E154" t="n">
-        <v>125.6</v>
+        <v>371.42</v>
       </c>
       <c r="F154" t="n">
-        <v>148.73</v>
+        <v>596.58</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>[27.62, 27.28, 26.95]</t>
+          <t>[13.37, 1023.27, 35.45]</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>[7.4, 175.4, 235.4]</t>
+          <t>[140.7, 58.1, 57.2]</t>
         </is>
       </c>
     </row>
@@ -6026,31 +6026,31 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>203.41</v>
+        <v>241.91</v>
       </c>
       <c r="E155" t="n">
-        <v>200.55</v>
+        <v>200.53</v>
       </c>
       <c r="F155" t="n">
-        <v>90.22</v>
+        <v>254.48</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>[21.63, 21.05, 20.47]</t>
+          <t>[424.53, 22.18, 79.65]</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>[175.4, 235.4, 254.0]</t>
+          <t>[58.1, 57.2, 279.8]</t>
         </is>
       </c>
     </row>
@@ -6062,31 +6062,31 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>182.04</v>
+        <v>98.84999999999999</v>
       </c>
       <c r="E156" t="n">
-        <v>171.67</v>
+        <v>58.57</v>
       </c>
       <c r="F156" t="n">
-        <v>83.02</v>
+        <v>37.62</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>[30.62, 30.49, 30.37]</t>
+          <t>[54.52, 108.62, 2.07]</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>[235.4, 254.0, 117.1]</t>
+          <t>[57.2, 279.8, 3.9]</t>
         </is>
       </c>
     </row>
@@ -6098,31 +6098,31 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>130.6</v>
+        <v>99.55</v>
       </c>
       <c r="E157" t="n">
-        <v>105.21</v>
+        <v>59.86</v>
       </c>
       <c r="F157" t="n">
-        <v>121.14</v>
+        <v>66.86</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>[42.37, 43.03, 43.73]</t>
+          <t>[107.47, 2.07, 11.33]</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>[254.0, 117.1, 13.8]</t>
+          <t>[279.8, 3.9, 5.9]</t>
         </is>
       </c>
     </row>
@@ -6134,31 +6134,31 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>65.15000000000001</v>
+        <v>39.56</v>
       </c>
       <c r="E158" t="n">
-        <v>44.97</v>
+        <v>25.52</v>
       </c>
       <c r="F158" t="n">
-        <v>97.53</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>[5.5, 0.05, 0.23]</t>
+          <t>[1.34, 11.68, 192.62]</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>[117.1, 13.8, 9.8]</t>
+          <t>[3.9, 5.9, 124.4]</t>
         </is>
       </c>
     </row>
@@ -6170,31 +6170,31 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>9.710000000000001</v>
+        <v>47.82</v>
       </c>
       <c r="E159" t="n">
-        <v>7.87</v>
+        <v>38.45</v>
       </c>
       <c r="F159" t="n">
-        <v>66.09</v>
+        <v>58.28</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>[0.03, 0.16, 140.49]</t>
+          <t>[11.93, 199.63, 314.3]</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>[13.8, 9.8, 140.7]</t>
+          <t>[5.9, 124.4, 280.2]</t>
         </is>
       </c>
     </row>
@@ -6206,31 +6206,31 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1446.16</v>
+        <v>46.08</v>
       </c>
       <c r="E160" t="n">
-        <v>863.58</v>
+        <v>41.82</v>
       </c>
       <c r="F160" t="n">
-        <v>1487.88</v>
+        <v>27.47</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>[0.05, 63.31, 2561.71]</t>
+          <t>[193.15, 304.35, 143.25]</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>[9.8, 140.7, 58.1]</t>
+          <t>[124.4, 280.2, 175.8]</t>
         </is>
       </c>
     </row>
@@ -6242,31 +6242,31 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>562.21</v>
+        <v>43.48</v>
       </c>
       <c r="E161" t="n">
-        <v>371.42</v>
+        <v>39.02</v>
       </c>
       <c r="F161" t="n">
-        <v>596.58</v>
+        <v>87.70999999999999</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>[13.37, 1023.27, 35.45]</t>
+          <t>[296.57, 138.35, 90.05]</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>[140.7, 58.1, 57.2]</t>
+          <t>[280.2, 175.8, 26.8]</t>
         </is>
       </c>
     </row>
@@ -6278,33 +6278,31 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>6.61</v>
+        <v>1781.99</v>
       </c>
       <c r="E162" t="n">
-        <v>6.61</v>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>1032.63</v>
+      </c>
+      <c r="F162" t="n">
+        <v>33242.14</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>[6.47, 6.61, 6.74]</t>
+          <t>[3089.59, 14.11, 0.0]</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[3.1, 8.7, 6.0]</t>
         </is>
       </c>
     </row>
@@ -6316,33 +6314,31 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>0.24</v>
+        <v>29.3</v>
       </c>
       <c r="E163" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>19.45</v>
+      </c>
+      <c r="F163" t="n">
+        <v>259.61</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>[0.28, 0.23, 0.19]</t>
+          <t>[59.06, 0.0, -0.0]</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[8.7, 6.0, 2.0]</t>
         </is>
       </c>
     </row>
@@ -6354,33 +6350,31 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>0.02</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="E164" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>6.87</v>
+      </c>
+      <c r="F164" t="n">
+        <v>99.98999999999999</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>[0.02, 0.01, 0.01]</t>
+          <t>[0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[6.0, 2.0, 12.6]</t>
         </is>
       </c>
     </row>
@@ -6392,19 +6386,19 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>0</v>
+        <v>7.37</v>
       </c>
       <c r="E165" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -6413,12 +6407,12 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[-0.0, -0.0, 0.46]</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[2.0, 12.6, 0.0]</t>
         </is>
       </c>
     </row>
@@ -6430,19 +6424,19 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>5.54</v>
+        <v>4534283.09</v>
       </c>
       <c r="E166" t="n">
-        <v>3.2</v>
+        <v>2617873.77</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -6451,12 +6445,12 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[-0.0, 0.01, 7853608.69]</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 9.6]</t>
+          <t>[12.6, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -6468,19 +6462,19 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>5.82</v>
+        <v>265042.76</v>
       </c>
       <c r="E167" t="n">
-        <v>4.23</v>
+        <v>153022.51</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -6489,12 +6483,12 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
+          <t>[-0.0, 459067.52, 0.0]</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
           <t>[0.0, 0.0, 0.0]</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>[0.0, 9.6, 3.1]</t>
         </is>
       </c>
     </row>
@@ -6506,31 +6500,33 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>77055.16</v>
+        <v>32219.81</v>
       </c>
       <c r="E168" t="n">
-        <v>44662.23</v>
-      </c>
-      <c r="F168" t="n">
-        <v>469024.27</v>
+        <v>18602.12</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>[133472.04, 523.87, 5.23]</t>
+          <t>[55806.35, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>[9.6, 3.1, 8.7]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -6542,31 +6538,33 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>1781.99</v>
+        <v>0</v>
       </c>
       <c r="E169" t="n">
-        <v>1032.63</v>
-      </c>
-      <c r="F169" t="n">
-        <v>33242.14</v>
+        <v>0</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>[3089.59, 14.11, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>[3.1, 8.7, 6.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -6578,31 +6576,33 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>29.3</v>
+        <v>0</v>
       </c>
       <c r="E170" t="n">
-        <v>19.45</v>
-      </c>
-      <c r="F170" t="n">
-        <v>259.61</v>
+        <v>0</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>[59.06, 0.0, -0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>[8.7, 6.0, 2.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -6614,31 +6614,33 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>8.140000000000001</v>
+        <v>5.47</v>
       </c>
       <c r="E171" t="n">
-        <v>6.87</v>
-      </c>
-      <c r="F171" t="n">
-        <v>99.98999999999999</v>
+        <v>3.16</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>[0.0, -0.0, -0.0]</t>
+          <t>[0.0, 0.0, 0.02]</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>[6.0, 2.0, 12.6]</t>
+          <t>[0.0, 0.0, 9.5]</t>
         </is>
       </c>
     </row>
@@ -6650,31 +6652,31 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>124.6</v>
+        <v>282.22</v>
       </c>
       <c r="E172" t="n">
-        <v>120.22</v>
+        <v>273.6</v>
       </c>
       <c r="F172" t="n">
-        <v>42.82</v>
+        <v>172.33</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>[396.03, 288.83, 422.56]</t>
+          <t>[470.71, 449.98, 550.18]</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>[252.7, 362.73, 279.14]</t>
+          <t>[146.9, 128.7, 374.48]</t>
         </is>
       </c>
     </row>
@@ -6686,31 +6688,31 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>142.54</v>
+        <v>203.57</v>
       </c>
       <c r="E173" t="n">
-        <v>135.05</v>
+        <v>197.36</v>
       </c>
       <c r="F173" t="n">
-        <v>44.16</v>
+        <v>90.8</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>[288.09, 424.88, 494.33]</t>
+          <t>[356.43, 501.49, 623.06]</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>[362.73, 279.14, 309.56]</t>
+          <t>[128.7, 374.48, 385.73]</t>
         </is>
       </c>
     </row>
@@ -6722,31 +6724,31 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>203.35</v>
+        <v>180.01</v>
       </c>
       <c r="E174" t="n">
-        <v>194.13</v>
+        <v>165.99</v>
       </c>
       <c r="F174" t="n">
-        <v>69.75</v>
+        <v>40.85</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>[415.28, 478.13, 539.57]</t>
+          <t>[444.84, 619.85, 642.85]</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>[279.14, 309.56, 261.9]</t>
+          <t>[374.48, 385.73, 449.35]</t>
         </is>
       </c>
     </row>
@@ -6758,31 +6760,31 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>268.2</v>
+        <v>383.85</v>
       </c>
       <c r="E175" t="n">
-        <v>263.51</v>
+        <v>329.03</v>
       </c>
       <c r="F175" t="n">
-        <v>124.36</v>
+        <v>80.11</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>[508.53, 582.42, 416.46]</t>
+          <t>[819.36, 950.62, 371.35]</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>[309.56, 261.9, 145.4]</t>
+          <t>[385.73, 449.35, 319.17]</t>
         </is>
       </c>
     </row>
@@ -6794,31 +6796,31 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>230.35</v>
+        <v>279.09</v>
       </c>
       <c r="E176" t="n">
-        <v>216.22</v>
+        <v>185.53</v>
       </c>
       <c r="F176" t="n">
-        <v>85.72</v>
+        <v>44.43</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>[578.27, 267.46, 611.34]</t>
+          <t>[929.6, 365.05, 283.31]</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>[261.9, 145.4, 401.1]</t>
+          <t>[449.35, 319.17, 252.85]</t>
         </is>
       </c>
     </row>
@@ -6830,31 +6832,31 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>187.02</v>
+        <v>83.77</v>
       </c>
       <c r="E177" t="n">
-        <v>177.47</v>
+        <v>65.62</v>
       </c>
       <c r="F177" t="n">
-        <v>98.84999999999999</v>
+        <v>26.43</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>[264.77, 555.76, 405.27]</t>
+          <t>[354.19, 275.77, 373.47]</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>[145.4, 401.1, 146.9]</t>
+          <t>[319.17, 252.85, 234.53]</t>
         </is>
       </c>
     </row>
@@ -6866,31 +6868,31 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>239.6</v>
+        <v>110.96</v>
       </c>
       <c r="E178" t="n">
-        <v>231.64</v>
+        <v>97.51000000000001</v>
       </c>
       <c r="F178" t="n">
-        <v>145.26</v>
+        <v>30.45</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>[546.77, 430.67, 394.18]</t>
+          <t>[275.56, 372.5, 428.09]</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>[401.1, 146.9, 128.7]</t>
+          <t>[252.85, 234.53, 559.95]</t>
         </is>
       </c>
     </row>
@@ -6902,31 +6904,31 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>282.22</v>
+        <v>162.28</v>
       </c>
       <c r="E179" t="n">
-        <v>273.6</v>
+        <v>146.67</v>
       </c>
       <c r="F179" t="n">
-        <v>172.33</v>
+        <v>30.54</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>[470.71, 449.98, 550.18]</t>
+          <t>[288.07, 339.64, 398.28]</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>[146.9, 128.7, 374.48]</t>
+          <t>[234.53, 559.95, 564.43]</t>
         </is>
       </c>
     </row>
@@ -6938,31 +6940,31 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>203.57</v>
+        <v>376.31</v>
       </c>
       <c r="E180" t="n">
-        <v>197.36</v>
+        <v>334.34</v>
       </c>
       <c r="F180" t="n">
-        <v>90.8</v>
+        <v>48.72</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>[356.43, 501.49, 623.06]</t>
+          <t>[325.39, 373.28, 242.66]</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>[128.7, 374.48, 385.73]</t>
+          <t>[559.95, 564.43, 819.96]</t>
         </is>
       </c>
     </row>
@@ -6974,31 +6976,31 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>180.01</v>
+        <v>381.98</v>
       </c>
       <c r="E181" t="n">
-        <v>165.99</v>
+        <v>339.71</v>
       </c>
       <c r="F181" t="n">
-        <v>40.85</v>
+        <v>41.32</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>[444.84, 619.85, 642.85]</t>
+          <t>[470.21, 333.85, 475.48]</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>[374.48, 385.73, 449.35]</t>
+          <t>[564.43, 819.96, 914.28]</t>
         </is>
       </c>
     </row>
@@ -7010,31 +7012,31 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>104.71</v>
+        <v>243.1</v>
       </c>
       <c r="E182" t="n">
-        <v>85.05</v>
+        <v>234.44</v>
       </c>
       <c r="F182" t="n">
-        <v>28.76</v>
+        <v>47.29</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>[178.85, 160.96, 205.04]</t>
+          <t>[198.95, 157.67, 551.72]</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>[277.85, 312.87, 200.81]</t>
+          <t>[397.76, 482.39, 731.53]</t>
         </is>
       </c>
     </row>
@@ -7046,31 +7048,31 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>75.38</v>
+        <v>260.33</v>
       </c>
       <c r="E183" t="n">
-        <v>63.35</v>
+        <v>248.78</v>
       </c>
       <c r="F183" t="n">
-        <v>25.77</v>
+        <v>47.18</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>[192.02, 240.21, 185.95]</t>
+          <t>[158.51, 588.04, 230.21]</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>[312.87, 200.81, 156.16]</t>
+          <t>[482.39, 731.53, 509.18]</t>
         </is>
       </c>
     </row>
@@ -7082,31 +7084,31 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>107.62</v>
+        <v>169.68</v>
       </c>
       <c r="E184" t="n">
-        <v>90.38</v>
+        <v>130.15</v>
       </c>
       <c r="F184" t="n">
-        <v>217.64</v>
+        <v>23.27</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>[255.79, 199.57, 201.64]</t>
+          <t>[612.67, 240.41, 360.47]</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>[200.81, 156.16, 28.9]</t>
+          <t>[731.53, 509.18, 363.28]</t>
         </is>
       </c>
     </row>
@@ -7118,31 +7120,31 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>123.27</v>
+        <v>203.08</v>
       </c>
       <c r="E185" t="n">
-        <v>105.02</v>
+        <v>168.27</v>
       </c>
       <c r="F185" t="n">
-        <v>251.24</v>
+        <v>36.78</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>[198.56, 222.77, 220.11]</t>
+          <t>[246.33, 371.65, 180.47]</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>[156.16, 28.9, 141.33]</t>
+          <t>[509.18, 363.28, 414.05]</t>
         </is>
       </c>
     </row>
@@ -7154,31 +7156,31 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>113.21</v>
+        <v>227.35</v>
       </c>
       <c r="E186" t="n">
-        <v>97.40000000000001</v>
+        <v>190.14</v>
       </c>
       <c r="F186" t="n">
-        <v>227.68</v>
+        <v>41.85</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>[205.5, 216.13, 255.0]</t>
+          <t>[386.83, 190.52, 173.48]</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>[28.9, 141.33, 214.21]</t>
+          <t>[363.28, 414.05, 496.82]</t>
         </is>
       </c>
     </row>
@@ -7190,31 +7192,31 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>116.89</v>
+        <v>360.38</v>
       </c>
       <c r="E187" t="n">
-        <v>80.56</v>
+        <v>344.52</v>
       </c>
       <c r="F187" t="n">
-        <v>25.92</v>
+        <v>62.79</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>[174.25, 205.02, 198.21]</t>
+          <t>[188.42, 171.42, 223.13]</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>[141.33, 214.21, 397.76]</t>
+          <t>[414.05, 496.82, 705.66]</t>
         </is>
       </c>
     </row>
@@ -7226,31 +7228,31 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>218.57</v>
+        <v>393.76</v>
       </c>
       <c r="E188" t="n">
-        <v>176.45</v>
+        <v>388.78</v>
       </c>
       <c r="F188" t="n">
-        <v>40.25</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>[205.47, 199.63, 159.92]</t>
+          <t>[182.16, 238.32, 190.16]</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>[214.21, 397.76, 482.39]</t>
+          <t>[496.82, 705.66, 574.51]</t>
         </is>
       </c>
     </row>
@@ -7262,31 +7264,31 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>243.1</v>
+        <v>453.63</v>
       </c>
       <c r="E189" t="n">
-        <v>234.44</v>
+        <v>448.25</v>
       </c>
       <c r="F189" t="n">
-        <v>47.29</v>
+        <v>68.33</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>[198.95, 157.67, 551.72]</t>
+          <t>[261.13, 209.71, 146.6]</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>[397.76, 482.39, 731.53]</t>
+          <t>[705.66, 574.51, 682.01]</t>
         </is>
       </c>
     </row>
@@ -7298,31 +7300,31 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>260.33</v>
+        <v>455.08</v>
       </c>
       <c r="E190" t="n">
-        <v>248.78</v>
+        <v>448.72</v>
       </c>
       <c r="F190" t="n">
-        <v>47.18</v>
+        <v>67.38</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>[158.51, 588.04, 230.21]</t>
+          <t>[230.82, 161.98, 247.7]</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>[482.39, 731.53, 509.18]</t>
+          <t>[574.51, 682.01, 730.13]</t>
         </is>
       </c>
     </row>
@@ -7334,31 +7336,31 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>169.68</v>
+        <v>553.25</v>
       </c>
       <c r="E191" t="n">
-        <v>130.15</v>
+        <v>547.36</v>
       </c>
       <c r="F191" t="n">
-        <v>23.27</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>[612.67, 240.41, 360.47]</t>
+          <t>[169.28, 259.36, 319.97]</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>[731.53, 509.18, 363.28]</t>
+          <t>[682.01, 730.13, 978.55]</t>
         </is>
       </c>
     </row>
@@ -7370,31 +7372,31 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>568.26</v>
+        <v>345.3</v>
       </c>
       <c r="E192" t="n">
-        <v>476.95</v>
+        <v>343.66</v>
       </c>
       <c r="F192" t="n">
-        <v>56.1</v>
+        <v>48.98</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>[140.5, 347.48, 283.62]</t>
+          <t>[329.85, 347.11, 395.52]</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>[891.03, 302.31, 918.78]</t>
+          <t>[700.6, 711.12, 691.74]</t>
         </is>
       </c>
     </row>
@@ -7406,31 +7408,31 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>339.84</v>
+        <v>312.74</v>
       </c>
       <c r="E193" t="n">
-        <v>222.34</v>
+        <v>307.24</v>
       </c>
       <c r="F193" t="n">
-        <v>27.58</v>
+        <v>44.67</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>[336.48, 333.04, 565.04]</t>
+          <t>[400.05, 457.87, 290.52]</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>[302.31, 918.78, 612.13]</t>
+          <t>[711.12, 691.74, 667.3]</t>
         </is>
       </c>
     </row>
@@ -7442,31 +7444,31 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>342.62</v>
+        <v>244.03</v>
       </c>
       <c r="E194" t="n">
-        <v>226.9</v>
+        <v>195.08</v>
       </c>
       <c r="F194" t="n">
-        <v>28.07</v>
+        <v>28.9</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>[328.93, 558.93, 295.44]</t>
+          <t>[475.27, 304.32, 559.56]</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>[918.78, 612.13, 333.1]</t>
+          <t>[691.74, 667.3, 565.34]</t>
         </is>
       </c>
     </row>
@@ -7478,31 +7480,31 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>80.79000000000001</v>
+        <v>388.82</v>
       </c>
       <c r="E195" t="n">
-        <v>76.37</v>
+        <v>314.24</v>
       </c>
       <c r="F195" t="n">
-        <v>20.52</v>
+        <v>42.18</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>[538.08, 287.78, 415.66]</t>
+          <t>[313.6, 581.49, 237.73]</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>[612.13, 333.1, 305.92]</t>
+          <t>[667.3, 565.34, 810.6]</t>
         </is>
       </c>
     </row>
@@ -7514,31 +7516,31 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>304.07</v>
+        <v>325.19</v>
       </c>
       <c r="E196" t="n">
-        <v>222.97</v>
+        <v>229.14</v>
       </c>
       <c r="F196" t="n">
-        <v>39.6</v>
+        <v>30.03</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>[286.22, 414.82, 229.26]</t>
+          <t>[611.95, 255.94, 555.49]</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>[333.1, 305.92, 742.4]</t>
+          <t>[565.34, 810.6, 641.64]</t>
         </is>
       </c>
     </row>
@@ -7550,31 +7552,31 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>368.01</v>
+        <v>363.12</v>
       </c>
       <c r="E197" t="n">
-        <v>327.71</v>
+        <v>309.16</v>
       </c>
       <c r="F197" t="n">
-        <v>52</v>
+        <v>39.3</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>[413.44, 229.12, 338.27]</t>
+          <t>[251.87, 545.02, 530.17]</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>[305.92, 742.4, 700.6]</t>
+          <t>[810.6, 641.64, 802.3]</t>
         </is>
       </c>
     </row>
@@ -7586,31 +7588,31 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>416.74</v>
+        <v>134.29</v>
       </c>
       <c r="E198" t="n">
-        <v>410.63</v>
+        <v>114.14</v>
       </c>
       <c r="F198" t="n">
-        <v>56.99</v>
+        <v>15.1</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>[231.26, 339.86, 351.11]</t>
+          <t>[575.01, 588.16, 811.72]</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>[742.4, 700.6, 711.12]</t>
+          <t>[641.64, 802.3, 750.07]</t>
         </is>
       </c>
     </row>
@@ -7622,31 +7624,31 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>345.3</v>
+        <v>161.11</v>
       </c>
       <c r="E199" t="n">
-        <v>343.66</v>
+        <v>155.71</v>
       </c>
       <c r="F199" t="n">
-        <v>48.98</v>
+        <v>20.17</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>[329.85, 347.11, 395.52]</t>
+          <t>[612.89, 847.56, 574.06]</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>[700.6, 711.12, 691.74]</t>
+          <t>[802.3, 750.07, 754.31]</t>
         </is>
       </c>
     </row>
@@ -7658,31 +7660,31 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>312.74</v>
+        <v>177.33</v>
       </c>
       <c r="E200" t="n">
-        <v>307.24</v>
+        <v>170.49</v>
       </c>
       <c r="F200" t="n">
-        <v>44.67</v>
+        <v>20.75</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>[400.05, 457.87, 290.52]</t>
+          <t>[860.63, 583.47, 695.6]</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>[711.12, 691.74, 667.3]</t>
+          <t>[750.07, 754.31, 925.67]</t>
         </is>
       </c>
     </row>
@@ -7694,31 +7696,31 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>244.03</v>
+        <v>190.53</v>
       </c>
       <c r="E201" t="n">
-        <v>195.08</v>
+        <v>187.75</v>
       </c>
       <c r="F201" t="n">
-        <v>28.9</v>
+        <v>24.39</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>[475.27, 304.32, 559.56]</t>
+          <t>[580.89, 693.0, 470.45]</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>[691.74, 667.3, 565.34]</t>
+          <t>[754.31, 925.67, 627.6]</t>
         </is>
       </c>
     </row>
